--- a/output/pdf_financials_xlsx/VTT.xlsx
+++ b/output/pdf_financials_xlsx/VTT.xlsx
@@ -1141,16 +1141,16 @@
         <v>0.110719</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-6.59638</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.009981</v>
+        <v>-0.723597</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.016269</v>
+        <v>-0.205169</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1387,22 +1387,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.356808</v>
+        <v>-0.356808</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.09445000000000001</v>
+        <v>-0.09445000000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-6.59638</v>
@@ -1534,22 +1534,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.356808</v>
+        <v>-0.356808</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.09445000000000001</v>
+        <v>-0.09445000000000001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-6.59638</v>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>11.8936</v>
+        <v>-11.8936</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4.7225</v>
+        <v>-4.7225</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>11.120125</v>
+        <v>-11.120125</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10.9368</v>
+        <v>-10.9368</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>13.78395</v>
+        <v>-13.78395</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>131.9276</v>
@@ -1750,16 +1750,16 @@
         <v>0.110719</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-6.59638</v>
@@ -1848,16 +1848,16 @@
         <v>0.110719</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-6.59638</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2.721183023482165</v>
+        <v>197.2788169765178</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>14.69395496707882</v>
+        <v>185.3060450329212</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -5322,39 +5322,37 @@
         <v>0.314731</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.314731</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.285438</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.285438</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.26791</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.624157</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.553167</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.553167</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.606242</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.606242</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.606242</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.606242</v>
       </c>
     </row>
     <row r="93">
@@ -8614,7 +8612,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9102,7 +9104,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -9528,7 +9534,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11582,7 +11592,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12600,7 +12614,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13118,7 +13136,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -35046,16 +35068,16 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>0.444805</v>
+        <v>-0.444805</v>
       </c>
       <c r="H326" s="5" t="n">
-        <v>0.218736</v>
+        <v>-0.218736</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>0.104295</v>
+        <v>-0.104295</v>
       </c>
       <c r="J326" s="5" t="n">
-        <v>0.275679</v>
+        <v>-0.275679</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
@@ -36922,10 +36944,10 @@
         </is>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.356808</v>
+        <v>-0.356808</v>
       </c>
       <c r="F348" s="5" t="n">
-        <v>0.09445000000000001</v>
+        <v>-0.09445000000000001</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VTT.xlsx
+++ b/output/pdf_financials_xlsx/VTT.xlsx
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006742</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>-0.275679</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.59638</v>
+        <v>-6.603122</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.149594</v>
@@ -1860,7 +1860,7 @@
         <v>-0.275679</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.59638</v>
+        <v>-6.603122</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.149594</v>
@@ -2106,45 +2106,43 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.16656</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.360133</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.091819</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.138529</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.018601</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.073041</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.076006</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.157286</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.253384</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.5168</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.285607</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.018314</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.18571</v>
       </c>
     </row>
     <row r="35">
@@ -2212,45 +2210,43 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.16656</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.360133</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.091819</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.138529</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.018601</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.073041</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.076006</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.157286</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.253384</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.5168</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.285607</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.018314</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.18571</v>
       </c>
     </row>
     <row r="37">
@@ -2865,28 +2861,28 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.128315</v>
+        <v>0.055274</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.098021</v>
+        <v>0.022015</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.178612</v>
+        <v>0.021326</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.257168</v>
+        <v>0.003784</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.537769</v>
+        <v>0.020969</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.315745</v>
+        <v>0.030138</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.028491</v>
+        <v>0.010177</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.193744</v>
+        <v>0.008033999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -6928,13 +6924,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003285</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019708</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040717</v>
       </c>
     </row>
     <row r="125">
@@ -6977,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003285</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019708</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040717</v>
       </c>
     </row>
     <row r="126">
@@ -7658,7 +7654,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11858,7 +11854,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14968,7 +14964,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -26130,7 +26130,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -34202,7 +34202,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">

--- a/output/pdf_financials_xlsx/VTT.xlsx
+++ b/output/pdf_financials_xlsx/VTT.xlsx
@@ -712,13 +712,13 @@
         <v>0.052846</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.97749</v>
+        <v>1.01949</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.527473</v>
+        <v>0.560473</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.479732</v>
+        <v>0.490232</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.289992</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.723597</v>
+        <v>0.009981</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.205169</v>
+        <v>0.016269</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>197.2788169765178</v>
+        <v>2.721183023482165</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>185.3060450329212</v>
+        <v>14.69395496707882</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4120,10 +4120,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.034386</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.054966</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4173,10 +4173,10 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.034386</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.054966</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0.032268</v>
@@ -4383,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.034386</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.054966</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -4659,15 +4659,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.005848728072585053</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01054395578467357</v>
       </c>
       <c r="O80" s="3" t="n">
         <v>0.006468826323400019</v>
@@ -5758,16 +5754,16 @@
         <v>-0.008536999999999999</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010325</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.009952000000000001</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.008014</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.00152</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>-0.011193</v>
@@ -6003,7 +5999,7 @@
         <v>-0.055215</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.03613</v>
+        <v>0.025805</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.268314</v>
@@ -8196,7 +8192,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -14802,7 +14802,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16818,7 +16822,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -21382,7 +21390,11 @@
           <t>GST / HST receivable</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -23172,7 +23184,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -24018,7 +24034,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E195" s="5" t="n">
         <v>-0.009981</v>
       </c>
@@ -30956,7 +30976,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -32408,7 +32432,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -36854,7 +36882,11 @@
           <t>Future income tax recovery (Note 5)</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E347" s="5" t="n">
         <v>-0.009981</v>
       </c>
